--- a/cashflow_templates/A_月次資金繰り表_28か月_入力中.xlsx
+++ b/cashflow_templates/A_月次資金繰り表_28か月_入力中.xlsx
@@ -351,7 +351,17 @@
     </comment>
     <comment ref="B9" authorId="1" shapeId="0">
       <text>
-        <t>2025年7〜9月：Drive「業績連動賞与/2025年分/7月・8月・9月」の集計ファイル（業績連動賞与_実績7〜9）が空（0バイト）で読み取れず未入力。</t>
+        <t>出典：Google Drive「業績連動賞与/2025年分/7月」【営業回覧用】業績連動賞与_実績7 の合計行「入金実績」</t>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="1" shapeId="0">
+      <text>
+        <t>出典：Google Drive「業績連動賞与/2025年分/8月」【営業回覧用】業績連動賞与_実績8 の合計行「入金実績」</t>
+      </text>
+    </comment>
+    <comment ref="D9" authorId="1" shapeId="0">
+      <text>
+        <t>出典：Google Drive「業績連動賞与/2025年分/9月」【営業回覧用】業績連動賞与_実績9 の合計行「入金実績」</t>
       </text>
     </comment>
     <comment ref="E9" authorId="1" shapeId="0">
@@ -1131,9 +1141,15 @@
           <t xml:space="preserve">  収入｜営業収入</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n"/>
-      <c r="C9" s="32" t="n"/>
-      <c r="D9" s="32" t="n"/>
+      <c r="B9" s="32" t="n">
+        <v>7564600</v>
+      </c>
+      <c r="C9" s="32" t="n">
+        <v>13195900</v>
+      </c>
+      <c r="D9" s="32" t="n">
+        <v>14169755</v>
+      </c>
       <c r="E9" s="32" t="n">
         <v>11571200</v>
       </c>
@@ -5889,7 +5905,7 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>※営業収入の2025年10月〜2026年8月はDrive集計ファイルの実績値（各セルのコメントに出典）。2025年7〜9月はDriveのファイルが空で未入力。2026年9月はユーザー入力値。</t>
+          <t>※営業収入の2025年7月〜2026年8月はDrive集計ファイル（業績連動賞与_実績N）の合計行「入金実績」（各セルのコメントに出典）。2026年9月は集計前のためユーザー入力値。</t>
         </is>
       </c>
     </row>
